--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -2657,7 +2657,7 @@
         <v>46277</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>46277.42946759259</v>
+        <v>46278.47149305556</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -2657,7 +2657,7 @@
         <v>46277</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>46278.47149305556</v>
+        <v>46279.50693287037</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2660,6 +2660,35 @@
         <v>46279.50693287037</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>87.98999999999999</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>46280.00109484954</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>46280.47258101852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2689,6 +2689,35 @@
         <v>46280.47258101852</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>46281.00137428241</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>46281</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>46281.46105324074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2718,6 +2718,35 @@
         <v>46281.46105324074</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>84.73999999999999</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>46282.00138805556</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>46282</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>46282.46805555555</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2747,6 +2747,35 @@
         <v>46282.46805555555</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>86.03</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>46283.00095988426</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>46283.44917824074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2776,6 +2776,35 @@
         <v>46283.44917824074</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>46284.00110758102</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>46284</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>46284.43820601852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -2802,7 +2802,7 @@
         <v>46284</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>46284.43820601852</v>
+        <v>46285.4537037037</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -2802,7 +2802,7 @@
         <v>46284</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>46285.4537037037</v>
+        <v>46286.51282407407</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2805,6 +2805,35 @@
         <v>46286.51282407407</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>46287.00123899306</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>46287.46569444444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2834,6 +2834,35 @@
         <v>46287.46569444444</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>86.73</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>46288.00128159722</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>46288</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>46288.45936342593</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2863,6 +2863,35 @@
         <v>46288.45936342593</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>46289.00125171297</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>46289.47229166667</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2892,6 +2892,35 @@
         <v>46289.47229166667</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>46290.00452934028</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>46290</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>46290.47584490741</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2921,6 +2921,35 @@
         <v>46290.47584490741</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>86.78</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>46291.0011503125</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>46291</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>46291.45871527777</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -2947,7 +2947,7 @@
         <v>46291</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>46291.45871527777</v>
+        <v>46292.48581018519</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -2947,7 +2947,7 @@
         <v>46291</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>46292.48581018519</v>
+        <v>46293.55194444444</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2950,6 +2950,35 @@
         <v>46293.55194444444</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>46294.00108199074</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>46294</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>46294.51569444445</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2979,6 +2979,35 @@
         <v>46294.51569444445</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>85.95</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>46295.0010990625</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>46295.50540509259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3008,6 +3008,35 @@
         <v>46295.50540509259</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>85.09</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>46296.00103694444</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>46296.52863425926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3037,6 +3037,35 @@
         <v>46296.52863425926</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>85.64</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>46297.00125177083</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>46297</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>46297.50402777778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3066,6 +3066,35 @@
         <v>46297.50402777778</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>84.42</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>46298.01161497685</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>46298</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>46298.47037037037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -3092,7 +3092,7 @@
         <v>46298</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>46298.47037037037</v>
+        <v>46299.49791666667</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -3092,7 +3092,7 @@
         <v>46298</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>46299.49791666667</v>
+        <v>46300.58173611111</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3095,6 +3095,35 @@
         <v>46300.58173611111</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>84.78</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>46302.0012677199</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>46302.53685185185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3124,6 +3124,35 @@
         <v>46302.53685185185</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>46303.00109519676</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>46303</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>46303.54275462963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3153,6 +3153,35 @@
         <v>46303.54275462963</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>46304.00109700231</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>46304</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>46304.53344907407</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3182,6 +3182,35 @@
         <v>46304.53344907407</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>86.94</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>46305.00458357639</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>46305.50427083333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -3208,7 +3208,7 @@
         <v>46305</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>46305.50427083333</v>
+        <v>46306.51384259259</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -3208,7 +3208,7 @@
         <v>46305</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>46306.51384259259</v>
+        <v>46307.61552083334</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3211,6 +3211,35 @@
         <v>46307.61552083334</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>88.34</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>46308.00116787037</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>46308.57497685185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3240,6 +3240,35 @@
         <v>46308.57497685185</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>46309.00444702547</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>46309.4759375</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3269,6 +3269,35 @@
         <v>46309.4759375</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>87.14</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>46310.00484304398</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>46310.46002314815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3298,6 +3298,35 @@
         <v>46310.46002314815</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>85.84</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>46311.00159416666</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>46311.456875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3327,6 +3327,35 @@
         <v>46311.456875</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>85.41</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>46312.00141601852</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>46312</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>46312.43021990741</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -3353,7 +3353,7 @@
         <v>46312</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>46312.43021990741</v>
+        <v>46313.44109953703</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -3353,7 +3353,7 @@
         <v>46312</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>46313.44109953703</v>
+        <v>46314.52185185185</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3356,6 +3356,35 @@
         <v>46314.52185185185</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>46315.00436684028</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>46315.46290509259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3385,6 +3385,35 @@
         <v>46315.46290509259</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>46316.00111878472</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>46316.47418981481</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3414,6 +3414,35 @@
         <v>46316.47418981481</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>85.91</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>46317.00110975694</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>46317.47403935185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3443,6 +3443,35 @@
         <v>46317.47403935185</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>86.47</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>46318.00110576389</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>46318</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>46318.4672337963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3472,6 +3472,35 @@
         <v>46318.4672337963</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>46319.00089826389</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>46319</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>46319.43842592592</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -3498,7 +3498,7 @@
         <v>46319</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>46319.43842592592</v>
+        <v>46320.45658564815</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -3498,7 +3498,7 @@
         <v>46319</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>46320.45658564815</v>
+        <v>46321.51998842593</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3501,6 +3501,35 @@
         <v>46321.51998842593</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>88.19</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>46322.00131067129</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>46322.4909837963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3530,6 +3530,35 @@
         <v>46322.4909837963</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>46323.00486894676</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>46323.51469907408</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3559,6 +3559,35 @@
         <v>46323.51469907408</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>46324.00127997685</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>46324.52091435185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3588,6 +3588,35 @@
         <v>46324.52091435185</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>46325.00129283564</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>46325.51521990741</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3617,6 +3617,35 @@
         <v>46325.51521990741</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>89.19</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>46326.02520778935</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>46326</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>46326.49489583333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
